--- a/student_assessment_forms/003_math_fractions_assessment--student_assessment_forms.xlsx
+++ b/student_assessment_forms/003_math_fractions_assessment--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is a fraction</t>
+          <t>What is a fraction?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>equivalent_fractions_2</t>
+          <t>what_are_equivalent_fractions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Equivalent Fractions</t>
+          <t>What are equivalent fractions?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fraction_addition</t>
+          <t>fraction_operation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fraction Addition</t>
+          <t>Fraction addition, subtraction, multiplication, and division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,228 +630,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fraction_subtraction</t>
+          <t>equivalent_fractions_operation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fraction Subtraction</t>
+          <t>Equivalent fractions, addition, subtraction, and division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>fraction_multiplication</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Fraction Multiplication</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>fraction_division</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Fraction Division</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>fraction_equivalent_1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>What are Equivalent Fractions</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>fraction_equivalent_2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>What are Equivalent Fractions</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>fraction_addition_1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Fraction Addition</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fraction_subtraction_1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fraction Subtraction</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fraction_multiplication_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Fraction Multiplication</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fraction_division_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fraction Division</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fraction_equivalent_2_1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What are Equivalent Fractions</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,10 +661,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -930,7 +723,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>equivalent_fractions_2_choices</t>
+          <t>what_are_equivalent_fractions_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,7 +740,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>equivalent_fractions_2_choices</t>
+          <t>what_are_equivalent_fractions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -964,7 +757,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fraction_equivalent_1_choices</t>
+          <t>equivalent_fractions_operation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -981,7 +774,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fraction_equivalent_1_choices</t>
+          <t>equivalent_fractions_operation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -990,74 +783,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>fraction_equivalent_2_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>fraction_equivalent_2_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>fraction_equivalent_2_1_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>fraction_equivalent_2_1_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
